--- a/liga_serie_A/datasets_liga_serie_A/links_times_cartola_liga_serie_A.xlsx
+++ b/liga_serie_A/datasets_liga_serie_A/links_times_cartola_liga_serie_A.xlsx
@@ -25,124 +25,124 @@
     <t>Link do Time</t>
   </si>
   <si>
+    <t>cartola scheuer17</t>
+  </si>
+  <si>
+    <t>Dom Camillo68</t>
+  </si>
+  <si>
+    <t>Fedato Futebol Clube</t>
+  </si>
+  <si>
+    <t>Gremiomaniasm</t>
+  </si>
+  <si>
+    <t>lsauer fc</t>
+  </si>
+  <si>
+    <t>MAFRA MARTINS FC</t>
+  </si>
+  <si>
+    <t>Paulo Virgili FC</t>
+  </si>
+  <si>
+    <t>pura bucha/internacional</t>
+  </si>
+  <si>
+    <t>seralex</t>
+  </si>
+  <si>
+    <t>Tatols Beants F.C</t>
+  </si>
+  <si>
+    <t>TEAM LOPES 99</t>
+  </si>
+  <si>
+    <t>Texas Club 2026</t>
+  </si>
+  <si>
+    <t>TIGRE LEON</t>
+  </si>
+  <si>
+    <t>VASCO MARTINS FC</t>
+  </si>
+  <si>
     <t>Atlético Colorado 2021</t>
   </si>
   <si>
-    <t>cartola scheuer17</t>
-  </si>
-  <si>
-    <t>Dom Camillo68</t>
-  </si>
-  <si>
     <t>FBC Colorado</t>
   </si>
   <si>
-    <t>Fedato Futebol Clube</t>
-  </si>
-  <si>
-    <t>Gremiomaniasm</t>
-  </si>
-  <si>
     <t>JV5 Tricolor Gaúcho</t>
   </si>
   <si>
-    <t>lsauer fc</t>
-  </si>
-  <si>
-    <t>MAFRA MARTINS FC</t>
-  </si>
-  <si>
     <t>Mau Humor F.C.</t>
   </si>
   <si>
-    <t>Paulo Virgili FC</t>
-  </si>
-  <si>
-    <t>pura bucha/internacional</t>
-  </si>
-  <si>
     <t>Rolo Compressor ZN</t>
   </si>
   <si>
-    <t>seralex</t>
-  </si>
-  <si>
-    <t>Tatols Beants F.C</t>
-  </si>
-  <si>
-    <t>TEAM LOPES 99</t>
-  </si>
-  <si>
-    <t>Texas Club 2026</t>
-  </si>
-  <si>
-    <t>TIGRE LEON</t>
-  </si>
-  <si>
     <t>TORRESMO COM PINGA PRO26.2</t>
   </si>
   <si>
-    <t>VASCO MARTINS FC</t>
+    <t>https://cartola.globo.com/#!/time/3851966</t>
+  </si>
+  <si>
+    <t>https://cartola.globo.com/#!/time/20696550</t>
+  </si>
+  <si>
+    <t>https://cartola.globo.com/#!/time/18642587</t>
+  </si>
+  <si>
+    <t>https://cartola.globo.com/#!/time/528730</t>
+  </si>
+  <si>
+    <t>https://cartola.globo.com/#!/time/44810918</t>
+  </si>
+  <si>
+    <t>https://cartola.globo.com/#!/time/4911779</t>
+  </si>
+  <si>
+    <t>https://cartola.globo.com/#!/time/14124559</t>
+  </si>
+  <si>
+    <t>https://cartola.globo.com/#!/time/18661583</t>
+  </si>
+  <si>
+    <t>https://cartola.globo.com/#!/time/29228373</t>
+  </si>
+  <si>
+    <t>https://cartola.globo.com/#!/time/212042</t>
+  </si>
+  <si>
+    <t>https://cartola.globo.com/#!/time/479510</t>
+  </si>
+  <si>
+    <t>https://cartola.globo.com/#!/time/1273719</t>
+  </si>
+  <si>
+    <t>https://cartola.globo.com/#!/time/3424598</t>
+  </si>
+  <si>
+    <t>https://cartola.globo.com/#!/time/14696986</t>
   </si>
   <si>
     <t>https://cartola.globo.com/#!/time/44574146</t>
   </si>
   <si>
-    <t>https://cartola.globo.com/#!/time/3851966</t>
-  </si>
-  <si>
-    <t>https://cartola.globo.com/#!/time/20696550</t>
-  </si>
-  <si>
     <t>https://cartola.globo.com/#!/time/186283</t>
   </si>
   <si>
-    <t>https://cartola.globo.com/#!/time/18642587</t>
-  </si>
-  <si>
-    <t>https://cartola.globo.com/#!/time/528730</t>
-  </si>
-  <si>
     <t>https://cartola.globo.com/#!/time/1747619</t>
   </si>
   <si>
-    <t>https://cartola.globo.com/#!/time/44810918</t>
-  </si>
-  <si>
-    <t>https://cartola.globo.com/#!/time/4911779</t>
-  </si>
-  <si>
     <t>https://cartola.globo.com/#!/time/19033717</t>
   </si>
   <si>
-    <t>https://cartola.globo.com/#!/time/14124559</t>
-  </si>
-  <si>
-    <t>https://cartola.globo.com/#!/time/18661583</t>
-  </si>
-  <si>
     <t>https://cartola.globo.com/#!/time/18223508</t>
   </si>
   <si>
-    <t>https://cartola.globo.com/#!/time/29228373</t>
-  </si>
-  <si>
-    <t>https://cartola.globo.com/#!/time/212042</t>
-  </si>
-  <si>
-    <t>https://cartola.globo.com/#!/time/479510</t>
-  </si>
-  <si>
-    <t>https://cartola.globo.com/#!/time/1273719</t>
-  </si>
-  <si>
-    <t>https://cartola.globo.com/#!/time/3424598</t>
-  </si>
-  <si>
     <t>https://cartola.globo.com/#!/time/49126346</t>
-  </si>
-  <si>
-    <t>https://cartola.globo.com/#!/time/14696986</t>
   </si>
 </sst>
 </file>
@@ -532,7 +532,7 @@
         <v>3</v>
       </c>
       <c r="B2">
-        <v>44574146</v>
+        <v>3851966</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>23</v>
@@ -543,7 +543,7 @@
         <v>4</v>
       </c>
       <c r="B3">
-        <v>3851966</v>
+        <v>20696550</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>24</v>
@@ -554,7 +554,7 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>20696550</v>
+        <v>18642587</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>25</v>
@@ -565,7 +565,7 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>186283</v>
+        <v>528730</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>26</v>
@@ -576,7 +576,7 @@
         <v>7</v>
       </c>
       <c r="B6">
-        <v>18642587</v>
+        <v>44810918</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>27</v>
@@ -587,7 +587,7 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>528730</v>
+        <v>4911779</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>28</v>
@@ -598,7 +598,7 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>1747619</v>
+        <v>14124559</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>29</v>
@@ -609,7 +609,7 @@
         <v>10</v>
       </c>
       <c r="B9">
-        <v>44810918</v>
+        <v>18661583</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>30</v>
@@ -620,7 +620,7 @@
         <v>11</v>
       </c>
       <c r="B10">
-        <v>4911779</v>
+        <v>29228373</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>31</v>
@@ -631,7 +631,7 @@
         <v>12</v>
       </c>
       <c r="B11">
-        <v>19033717</v>
+        <v>212042</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>32</v>
@@ -642,7 +642,7 @@
         <v>13</v>
       </c>
       <c r="B12">
-        <v>14124559</v>
+        <v>479510</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>33</v>
@@ -653,7 +653,7 @@
         <v>14</v>
       </c>
       <c r="B13">
-        <v>18661583</v>
+        <v>1273719</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>34</v>
@@ -664,7 +664,7 @@
         <v>15</v>
       </c>
       <c r="B14">
-        <v>18223508</v>
+        <v>3424598</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>35</v>
@@ -675,7 +675,7 @@
         <v>16</v>
       </c>
       <c r="B15">
-        <v>29228373</v>
+        <v>14696986</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>36</v>
@@ -686,7 +686,7 @@
         <v>17</v>
       </c>
       <c r="B16">
-        <v>212042</v>
+        <v>44574146</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>37</v>
@@ -697,7 +697,7 @@
         <v>18</v>
       </c>
       <c r="B17">
-        <v>479510</v>
+        <v>186283</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>38</v>
@@ -708,7 +708,7 @@
         <v>19</v>
       </c>
       <c r="B18">
-        <v>1273719</v>
+        <v>1747619</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>39</v>
@@ -719,7 +719,7 @@
         <v>20</v>
       </c>
       <c r="B19">
-        <v>3424598</v>
+        <v>19033717</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>40</v>
@@ -730,7 +730,7 @@
         <v>21</v>
       </c>
       <c r="B20">
-        <v>49126346</v>
+        <v>18223508</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>41</v>
@@ -741,7 +741,7 @@
         <v>22</v>
       </c>
       <c r="B21">
-        <v>14696986</v>
+        <v>49126346</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>42</v>
@@ -749,26 +749,26 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" location="!/time/44574146"/>
-    <hyperlink ref="C3" r:id="rId2" location="!/time/3851966"/>
-    <hyperlink ref="C4" r:id="rId3" location="!/time/20696550"/>
-    <hyperlink ref="C5" r:id="rId4" location="!/time/186283"/>
-    <hyperlink ref="C6" r:id="rId5" location="!/time/18642587"/>
-    <hyperlink ref="C7" r:id="rId6" location="!/time/528730"/>
-    <hyperlink ref="C8" r:id="rId7" location="!/time/1747619"/>
-    <hyperlink ref="C9" r:id="rId8" location="!/time/44810918"/>
-    <hyperlink ref="C10" r:id="rId9" location="!/time/4911779"/>
-    <hyperlink ref="C11" r:id="rId10" location="!/time/19033717"/>
-    <hyperlink ref="C12" r:id="rId11" location="!/time/14124559"/>
-    <hyperlink ref="C13" r:id="rId12" location="!/time/18661583"/>
-    <hyperlink ref="C14" r:id="rId13" location="!/time/18223508"/>
-    <hyperlink ref="C15" r:id="rId14" location="!/time/29228373"/>
-    <hyperlink ref="C16" r:id="rId15" location="!/time/212042"/>
-    <hyperlink ref="C17" r:id="rId16" location="!/time/479510"/>
-    <hyperlink ref="C18" r:id="rId17" location="!/time/1273719"/>
-    <hyperlink ref="C19" r:id="rId18" location="!/time/3424598"/>
-    <hyperlink ref="C20" r:id="rId19" location="!/time/49126346"/>
-    <hyperlink ref="C21" r:id="rId20" location="!/time/14696986"/>
+    <hyperlink ref="C2" r:id="rId1" location="!/time/3851966"/>
+    <hyperlink ref="C3" r:id="rId2" location="!/time/20696550"/>
+    <hyperlink ref="C4" r:id="rId3" location="!/time/18642587"/>
+    <hyperlink ref="C5" r:id="rId4" location="!/time/528730"/>
+    <hyperlink ref="C6" r:id="rId5" location="!/time/44810918"/>
+    <hyperlink ref="C7" r:id="rId6" location="!/time/4911779"/>
+    <hyperlink ref="C8" r:id="rId7" location="!/time/14124559"/>
+    <hyperlink ref="C9" r:id="rId8" location="!/time/18661583"/>
+    <hyperlink ref="C10" r:id="rId9" location="!/time/29228373"/>
+    <hyperlink ref="C11" r:id="rId10" location="!/time/212042"/>
+    <hyperlink ref="C12" r:id="rId11" location="!/time/479510"/>
+    <hyperlink ref="C13" r:id="rId12" location="!/time/1273719"/>
+    <hyperlink ref="C14" r:id="rId13" location="!/time/3424598"/>
+    <hyperlink ref="C15" r:id="rId14" location="!/time/14696986"/>
+    <hyperlink ref="C16" r:id="rId15" location="!/time/44574146"/>
+    <hyperlink ref="C17" r:id="rId16" location="!/time/186283"/>
+    <hyperlink ref="C18" r:id="rId17" location="!/time/1747619"/>
+    <hyperlink ref="C19" r:id="rId18" location="!/time/19033717"/>
+    <hyperlink ref="C20" r:id="rId19" location="!/time/18223508"/>
+    <hyperlink ref="C21" r:id="rId20" location="!/time/49126346"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/liga_serie_A/datasets_liga_serie_A/links_times_cartola_liga_serie_A.xlsx
+++ b/liga_serie_A/datasets_liga_serie_A/links_times_cartola_liga_serie_A.xlsx
@@ -25,30 +25,45 @@
     <t>Link do Time</t>
   </si>
   <si>
+    <t>Atlético Colorado 2021</t>
+  </si>
+  <si>
     <t>cartola scheuer17</t>
   </si>
   <si>
     <t>Dom Camillo68</t>
   </si>
   <si>
+    <t>FBC Colorado</t>
+  </si>
+  <si>
     <t>Fedato Futebol Clube</t>
   </si>
   <si>
     <t>Gremiomaniasm</t>
   </si>
   <si>
+    <t>JV5 Tricolor Gaúcho</t>
+  </si>
+  <si>
     <t>lsauer fc</t>
   </si>
   <si>
     <t>MAFRA MARTINS FC</t>
   </si>
   <si>
+    <t>Mau Humor F.C.</t>
+  </si>
+  <si>
     <t>Paulo Virgili FC</t>
   </si>
   <si>
     <t>pura bucha/internacional</t>
   </si>
   <si>
+    <t>Rolo Compressor ZN</t>
+  </si>
+  <si>
     <t>seralex</t>
   </si>
   <si>
@@ -64,25 +79,13 @@
     <t>TIGRE LEON</t>
   </si>
   <si>
+    <t>TORRESMO COM PINGA PRO26.2</t>
+  </si>
+  <si>
     <t>VASCO MARTINS FC</t>
   </si>
   <si>
-    <t>Atlético Colorado 2021</t>
-  </si>
-  <si>
-    <t>FBC Colorado</t>
-  </si>
-  <si>
-    <t>JV5 Tricolor Gaúcho</t>
-  </si>
-  <si>
-    <t>Mau Humor F.C.</t>
-  </si>
-  <si>
-    <t>Rolo Compressor ZN</t>
-  </si>
-  <si>
-    <t>TORRESMO COM PINGA PRO26.2</t>
+    <t>https://cartola.globo.com/#!/time/44574146</t>
   </si>
   <si>
     <t>https://cartola.globo.com/#!/time/3851966</t>
@@ -91,24 +94,36 @@
     <t>https://cartola.globo.com/#!/time/20696550</t>
   </si>
   <si>
+    <t>https://cartola.globo.com/#!/time/186283</t>
+  </si>
+  <si>
     <t>https://cartola.globo.com/#!/time/18642587</t>
   </si>
   <si>
     <t>https://cartola.globo.com/#!/time/528730</t>
   </si>
   <si>
+    <t>https://cartola.globo.com/#!/time/1747619</t>
+  </si>
+  <si>
     <t>https://cartola.globo.com/#!/time/44810918</t>
   </si>
   <si>
     <t>https://cartola.globo.com/#!/time/4911779</t>
   </si>
   <si>
+    <t>https://cartola.globo.com/#!/time/19033717</t>
+  </si>
+  <si>
     <t>https://cartola.globo.com/#!/time/14124559</t>
   </si>
   <si>
     <t>https://cartola.globo.com/#!/time/18661583</t>
   </si>
   <si>
+    <t>https://cartola.globo.com/#!/time/18223508</t>
+  </si>
+  <si>
     <t>https://cartola.globo.com/#!/time/29228373</t>
   </si>
   <si>
@@ -124,25 +139,10 @@
     <t>https://cartola.globo.com/#!/time/3424598</t>
   </si>
   <si>
+    <t>https://cartola.globo.com/#!/time/49126346</t>
+  </si>
+  <si>
     <t>https://cartola.globo.com/#!/time/14696986</t>
-  </si>
-  <si>
-    <t>https://cartola.globo.com/#!/time/44574146</t>
-  </si>
-  <si>
-    <t>https://cartola.globo.com/#!/time/186283</t>
-  </si>
-  <si>
-    <t>https://cartola.globo.com/#!/time/1747619</t>
-  </si>
-  <si>
-    <t>https://cartola.globo.com/#!/time/19033717</t>
-  </si>
-  <si>
-    <t>https://cartola.globo.com/#!/time/18223508</t>
-  </si>
-  <si>
-    <t>https://cartola.globo.com/#!/time/49126346</t>
   </si>
 </sst>
 </file>
@@ -532,7 +532,7 @@
         <v>3</v>
       </c>
       <c r="B2">
-        <v>3851966</v>
+        <v>44574146</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>23</v>
@@ -543,7 +543,7 @@
         <v>4</v>
       </c>
       <c r="B3">
-        <v>20696550</v>
+        <v>3851966</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>24</v>
@@ -554,7 +554,7 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>18642587</v>
+        <v>20696550</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>25</v>
@@ -565,7 +565,7 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>528730</v>
+        <v>186283</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>26</v>
@@ -576,7 +576,7 @@
         <v>7</v>
       </c>
       <c r="B6">
-        <v>44810918</v>
+        <v>18642587</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>27</v>
@@ -587,7 +587,7 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>4911779</v>
+        <v>528730</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>28</v>
@@ -598,7 +598,7 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>14124559</v>
+        <v>1747619</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>29</v>
@@ -609,7 +609,7 @@
         <v>10</v>
       </c>
       <c r="B9">
-        <v>18661583</v>
+        <v>44810918</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>30</v>
@@ -620,7 +620,7 @@
         <v>11</v>
       </c>
       <c r="B10">
-        <v>29228373</v>
+        <v>4911779</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>31</v>
@@ -631,7 +631,7 @@
         <v>12</v>
       </c>
       <c r="B11">
-        <v>212042</v>
+        <v>19033717</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>32</v>
@@ -642,7 +642,7 @@
         <v>13</v>
       </c>
       <c r="B12">
-        <v>479510</v>
+        <v>14124559</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>33</v>
@@ -653,7 +653,7 @@
         <v>14</v>
       </c>
       <c r="B13">
-        <v>1273719</v>
+        <v>18661583</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>34</v>
@@ -664,7 +664,7 @@
         <v>15</v>
       </c>
       <c r="B14">
-        <v>3424598</v>
+        <v>18223508</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>35</v>
@@ -675,7 +675,7 @@
         <v>16</v>
       </c>
       <c r="B15">
-        <v>14696986</v>
+        <v>29228373</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>36</v>
@@ -686,7 +686,7 @@
         <v>17</v>
       </c>
       <c r="B16">
-        <v>44574146</v>
+        <v>212042</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>37</v>
@@ -697,7 +697,7 @@
         <v>18</v>
       </c>
       <c r="B17">
-        <v>186283</v>
+        <v>479510</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>38</v>
@@ -708,7 +708,7 @@
         <v>19</v>
       </c>
       <c r="B18">
-        <v>1747619</v>
+        <v>1273719</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>39</v>
@@ -719,7 +719,7 @@
         <v>20</v>
       </c>
       <c r="B19">
-        <v>19033717</v>
+        <v>3424598</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>40</v>
@@ -730,7 +730,7 @@
         <v>21</v>
       </c>
       <c r="B20">
-        <v>18223508</v>
+        <v>49126346</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>41</v>
@@ -741,7 +741,7 @@
         <v>22</v>
       </c>
       <c r="B21">
-        <v>49126346</v>
+        <v>14696986</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>42</v>
@@ -749,26 +749,26 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" location="!/time/3851966"/>
-    <hyperlink ref="C3" r:id="rId2" location="!/time/20696550"/>
-    <hyperlink ref="C4" r:id="rId3" location="!/time/18642587"/>
-    <hyperlink ref="C5" r:id="rId4" location="!/time/528730"/>
-    <hyperlink ref="C6" r:id="rId5" location="!/time/44810918"/>
-    <hyperlink ref="C7" r:id="rId6" location="!/time/4911779"/>
-    <hyperlink ref="C8" r:id="rId7" location="!/time/14124559"/>
-    <hyperlink ref="C9" r:id="rId8" location="!/time/18661583"/>
-    <hyperlink ref="C10" r:id="rId9" location="!/time/29228373"/>
-    <hyperlink ref="C11" r:id="rId10" location="!/time/212042"/>
-    <hyperlink ref="C12" r:id="rId11" location="!/time/479510"/>
-    <hyperlink ref="C13" r:id="rId12" location="!/time/1273719"/>
-    <hyperlink ref="C14" r:id="rId13" location="!/time/3424598"/>
-    <hyperlink ref="C15" r:id="rId14" location="!/time/14696986"/>
-    <hyperlink ref="C16" r:id="rId15" location="!/time/44574146"/>
-    <hyperlink ref="C17" r:id="rId16" location="!/time/186283"/>
-    <hyperlink ref="C18" r:id="rId17" location="!/time/1747619"/>
-    <hyperlink ref="C19" r:id="rId18" location="!/time/19033717"/>
-    <hyperlink ref="C20" r:id="rId19" location="!/time/18223508"/>
-    <hyperlink ref="C21" r:id="rId20" location="!/time/49126346"/>
+    <hyperlink ref="C2" r:id="rId1" location="!/time/44574146"/>
+    <hyperlink ref="C3" r:id="rId2" location="!/time/3851966"/>
+    <hyperlink ref="C4" r:id="rId3" location="!/time/20696550"/>
+    <hyperlink ref="C5" r:id="rId4" location="!/time/186283"/>
+    <hyperlink ref="C6" r:id="rId5" location="!/time/18642587"/>
+    <hyperlink ref="C7" r:id="rId6" location="!/time/528730"/>
+    <hyperlink ref="C8" r:id="rId7" location="!/time/1747619"/>
+    <hyperlink ref="C9" r:id="rId8" location="!/time/44810918"/>
+    <hyperlink ref="C10" r:id="rId9" location="!/time/4911779"/>
+    <hyperlink ref="C11" r:id="rId10" location="!/time/19033717"/>
+    <hyperlink ref="C12" r:id="rId11" location="!/time/14124559"/>
+    <hyperlink ref="C13" r:id="rId12" location="!/time/18661583"/>
+    <hyperlink ref="C14" r:id="rId13" location="!/time/18223508"/>
+    <hyperlink ref="C15" r:id="rId14" location="!/time/29228373"/>
+    <hyperlink ref="C16" r:id="rId15" location="!/time/212042"/>
+    <hyperlink ref="C17" r:id="rId16" location="!/time/479510"/>
+    <hyperlink ref="C18" r:id="rId17" location="!/time/1273719"/>
+    <hyperlink ref="C19" r:id="rId18" location="!/time/3424598"/>
+    <hyperlink ref="C20" r:id="rId19" location="!/time/49126346"/>
+    <hyperlink ref="C21" r:id="rId20" location="!/time/14696986"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
